--- a/Assets/Project/Csv/Fish/FishTable.xlsx
+++ b/Assets/Project/Csv/Fish/FishTable.xlsx
@@ -1,158 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Fish\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D57EC0-0D8D-46E8-89D7-765B21093523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="125725" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>enum Grade</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>필드(속성)</t>
-  </si>
-  <si>
-    <t>소문자로 시작</t>
-  </si>
-  <si>
-    <t>Anchovy</t>
-  </si>
-  <si>
-    <t>private</t>
-  </si>
-  <si>
-    <t>_소문자로 시작</t>
-  </si>
-  <si>
-    <t>Sea snake</t>
-  </si>
-  <si>
-    <t>Seahorse</t>
-  </si>
-  <si>
-    <t>Frog</t>
-  </si>
-  <si>
-    <t>프로퍼티, 함수</t>
-  </si>
-  <si>
-    <t>대문자로 시작</t>
-  </si>
-  <si>
-    <t>{id/int/UNIQUE/NOT NULL}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{name/string/UNIQUE/NOT NULL}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{grade/enum/CHECK IN(0|1|2|3|Normal|Low|Mid|High)}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{weight/int/NOT NULL/CHECK(VALUE &gt; 0)}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Low</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>High</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="2" tint="-0.09997863704336681"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
+        <fgColor theme="3" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
+        <fgColor theme="3" tint="0.8999908444471572"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -182,57 +104,116 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -270,7 +251,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -304,7 +285,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -339,10 +319,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -515,161 +494,231 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="26.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="2" bestFit="1" customWidth="1"/>
+    <col width="26.625" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="32.875" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="52.625" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="41.75" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="14.125" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="13.75" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>{id/int/UNIQUE/NOT NULL}</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>{name/string/UNIQUE/NOT NULL}</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>{grade/enum/CHECK IN(0|1|2|3|Normal|Low|Mid|High)}</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>{weight/int/NOT NULL/CHECK(VALUE &gt; 0)}</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>enum Grade</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>필드(속성)</t>
+        </is>
+      </c>
+      <c r="L1" s="0" t="inlineStr">
+        <is>
+          <t>소문자로 시작</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="2">
+      <c r="A2" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Anchovy</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="D2" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>_소문자로 시작</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Bream</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Sea snake</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Seahorse</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>프로퍼티, 함수</t>
+        </is>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t>대문자로 시작</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
-        <v>2000</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
-        <v>2100</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5">
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Frog</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="5">
-        <v>100</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
-        <v>2200</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="6">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
-        <v>2300</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="7">
-        <v>3</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="1">
-        <v>3</v>
-      </c>
-      <c r="K5" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" t="s">
-        <v>11</v>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="200" verticalDpi="200"/>
 </worksheet>
 </file>